--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6251,0.0073,0.4460,0.0014</t>
-  </si>
-  <si>
-    <t>0.4191,0.0073,0.1357,0.2467</t>
-  </si>
-  <si>
-    <t>0.8271,0.0168,0.1355,0.0037</t>
-  </si>
-  <si>
-    <t>0.7046,0.0077,0.2490,0.0129</t>
-  </si>
-  <si>
-    <t>0.9846,0.0101,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9901,0.0070,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9880,0.0087,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0080,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9814,0.0151,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9826,0.0152,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9890,0.0079,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9892,0.0073,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.5029,0.0059,0.6119,0.0002</t>
-  </si>
-  <si>
-    <t>0.3158,0.0052,0.7770,0.0001</t>
-  </si>
-  <si>
-    <t>0.0730,0.0082,0.9452,0.0001</t>
-  </si>
-  <si>
-    <t>0.2885,0.0069,0.7893,0.0001</t>
-  </si>
-  <si>
-    <t>0.4294,0.0059,0.6752,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.9921,0.0065,0.0000</t>
-  </si>
-  <si>
-    <t>0.0128,0.9761,0.0154,0.0001</t>
-  </si>
-  <si>
-    <t>0.4199,0.5975,0.0187,0.0004</t>
-  </si>
-  <si>
-    <t>0.0229,0.9638,0.0139,0.0002</t>
-  </si>
-  <si>
-    <t>0.0047,0.9932,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.1557,0.0062,0.8865,0.0002</t>
-  </si>
-  <si>
-    <t>0.2479,0.0122,0.8040,0.0003</t>
-  </si>
-  <si>
-    <t>0.0216,0.0041,0.9803,0.0002</t>
-  </si>
-  <si>
-    <t>0.0312,0.0024,0.9782,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.0033,0.9920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0158,0.0037,0.9864,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.2008,0.6313,0.0732,0.0015</t>
-  </si>
-  <si>
-    <t>0.6760,0.0151,0.3543,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.3276,0.0180,0.6776,0.0001</t>
-  </si>
-  <si>
-    <t>0.8065,0.0597,0.0988,0.0008</t>
-  </si>
-  <si>
-    <t>0.1858,0.0614,0.7947,0.0007</t>
-  </si>
-  <si>
-    <t>0.6057,0.2821,0.0604,0.0008</t>
-  </si>
-  <si>
-    <t>0.0634,0.9133,0.0271,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.9846,0.3431,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.4492,0.9813,0.0001</t>
-  </si>
-  <si>
-    <t>0.0141,0.2415,0.9270,0.0006</t>
-  </si>
-  <si>
-    <t>0.0114,0.0051,0.9861,0.0012</t>
-  </si>
-  <si>
-    <t>0.0229,0.0406,0.9611,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9859,0.0936,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.0318,0.9887,0.0001</t>
-  </si>
-  <si>
-    <t>0.4925,0.1634,0.2781,0.0163</t>
-  </si>
-  <si>
-    <t>0.0069,0.9834,0.0121,0.0006</t>
-  </si>
-  <si>
-    <t>0.0021,0.9871,0.0381,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9984,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.4262,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0456,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.0137,0.9903,0.0001</t>
-  </si>
-  <si>
-    <t>0.0044,0.0019,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0094,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0061,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.9356,0.0420,0.0153,0.0002</t>
-  </si>
-  <si>
-    <t>0.9463,0.0181,0.0266,0.0003</t>
-  </si>
-  <si>
-    <t>0.9644,0.0202,0.0105,0.0003</t>
-  </si>
-  <si>
-    <t>0.0027,0.0150,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.9375,0.0340,0.0200,0.0003</t>
-  </si>
-  <si>
-    <t>0.9586,0.0271,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9322,0.0483,0.0139,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9567,0.9721,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0315,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.2548,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8768,0.9551,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0045,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0159,0.9718,0.0109,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9987,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.4975,0.0065,0.6184,0.0003</t>
-  </si>
-  <si>
-    <t>0.5807,0.0184,0.4607,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0032,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7755,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.7411,0.9525,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9808,0.4509,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9931,0.5509,0.0000</t>
-  </si>
-  <si>
-    <t>0.6186,0.0058,0.4340,0.0028</t>
-  </si>
-  <si>
-    <t>0.0155,0.0033,0.0151,0.9880</t>
-  </si>
-  <si>
-    <t>0.3253,0.0062,0.0752,0.4730</t>
-  </si>
-  <si>
-    <t>0.3095,0.0051,0.1225,0.4251</t>
-  </si>
-  <si>
-    <t>0.3371,0.0054,0.1778,0.3054</t>
-  </si>
-  <si>
-    <t>0.0160,0.0030,0.0208,0.9865</t>
-  </si>
-  <si>
-    <t>0.0002,0.9526,0.8952,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.5265,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.8309,0.9462,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9232,0.8615,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.8667,0.8822,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.6390,0.9360,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0083,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9817,0.0140,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.9736,0.0229,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9812,0.0153,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9794,0.0160,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.9846,0.0132,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9567,0.0355,0.0078,0.0003</t>
-  </si>
-  <si>
-    <t>0.9718,0.0194,0.0065,0.0002</t>
-  </si>
-  <si>
-    <t>0.9882,0.0076,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9816,0.0140,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.9875,0.0085,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9872,0.0093,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9895,0.0078,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9827,0.0137,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.9841,0.0111,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9841,0.0117,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0082,0.0072,0.9910,0.0001</t>
-  </si>
-  <si>
-    <t>0.5969,0.0056,0.4775,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0014,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0280,0.9705,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.0120,0.9849,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.0836,0.8887,0.0230,0.0003</t>
-  </si>
-  <si>
-    <t>0.2308,0.7090,0.0302,0.0005</t>
-  </si>
-  <si>
-    <t>0.0270,0.9694,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0155,0.9807,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.4846,0.3390,0.0749,0.0008</t>
-  </si>
-  <si>
-    <t>0.4764,0.0066,0.6250,0.0003</t>
-  </si>
-  <si>
-    <t>0.0683,0.0041,0.9512,0.0001</t>
-  </si>
-  <si>
-    <t>0.5823,0.0168,0.4591,0.0006</t>
-  </si>
-  <si>
-    <t>0.2906,0.0088,0.7641,0.0005</t>
-  </si>
-  <si>
-    <t>0.5542,0.0553,0.3801,0.0229</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9960,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.0716,0.9181,0.0161,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.9986,0.0276,0.0000</t>
-  </si>
-  <si>
-    <t>0.0914,0.9007,0.0138,0.0002</t>
-  </si>
-  <si>
-    <t>0.6017,0.1422,0.1580,0.0007</t>
-  </si>
-  <si>
-    <t>0.4156,0.5269,0.0368,0.0008</t>
-  </si>
-  <si>
-    <t>0.9626,0.0197,0.0110,0.0001</t>
-  </si>
-  <si>
-    <t>0.9650,0.0160,0.0122,0.0003</t>
-  </si>
-  <si>
-    <t>0.9727,0.0168,0.0062,0.0004</t>
-  </si>
-  <si>
-    <t>0.9317,0.0234,0.0349,0.0005</t>
-  </si>
-  <si>
-    <t>0.9631,0.0243,0.0088,0.0003</t>
-  </si>
-  <si>
-    <t>0.8786,0.0612,0.0352,0.0002</t>
-  </si>
-  <si>
-    <t>0.9791,0.0144,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.9632,0.0259,0.0075,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.8216,0.9764,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3666,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0077,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0866,0.9921,0.0002</t>
-  </si>
-  <si>
-    <t>0.5485,0.0034,0.5788,0.0002</t>
-  </si>
-  <si>
-    <t>0.5517,0.0161,0.5092,0.0009</t>
-  </si>
-  <si>
-    <t>0.0783,0.0018,0.9478,0.0001</t>
-  </si>
-  <si>
-    <t>0.6333,0.0062,0.4503,0.0003</t>
-  </si>
-  <si>
-    <t>0.6786,0.0053,0.3376,0.0045</t>
-  </si>
-  <si>
-    <t>0.0031,0.0012,0.0051,0.9978</t>
-  </si>
-  <si>
-    <t>0.0386,0.0122,0.0216,0.9668</t>
-  </si>
-  <si>
-    <t>0.4099,0.0033,0.1399,0.2435</t>
-  </si>
-  <si>
-    <t>0.0000,0.8813,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.9538,0.0299,0.0113,0.0004</t>
-  </si>
-  <si>
-    <t>0.2973,0.2320,0.4286,0.0049</t>
-  </si>
-  <si>
-    <t>0.9489,0.0152,0.0253,0.0004</t>
-  </si>
-  <si>
-    <t>0.5471,0.3398,0.0518,0.0007</t>
-  </si>
-  <si>
-    <t>0.9607,0.0107,0.0140,0.0006</t>
-  </si>
-  <si>
-    <t>0.7140,0.0111,0.3268,0.0013</t>
-  </si>
-  <si>
-    <t>0.9610,0.0136,0.0132,0.0007</t>
-  </si>
-  <si>
-    <t>0.0094,0.0480,0.9824,0.0002</t>
-  </si>
-  <si>
-    <t>0.7918,0.0112,0.2275,0.0006</t>
-  </si>
-  <si>
-    <t>0.8570,0.0344,0.0889,0.0006</t>
-  </si>
-  <si>
-    <t>0.4110,0.3406,0.0881,0.0007</t>
-  </si>
-  <si>
-    <t>0.7481,0.0642,0.1421,0.0012</t>
-  </si>
-  <si>
-    <t>0.6234,0.0359,0.3594,0.0006</t>
-  </si>
-  <si>
-    <t>0.4450,0.0963,0.4141,0.0017</t>
-  </si>
-  <si>
-    <t>0.1901,0.0233,0.8263,0.0003</t>
-  </si>
-  <si>
-    <t>0.7131,0.0328,0.2458,0.0011</t>
-  </si>
-  <si>
-    <t>0.9832,0.0095,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.9837,0.0100,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9771,0.0121,0.0054,0.0003</t>
-  </si>
-  <si>
-    <t>0.9790,0.0096,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.9787,0.0111,0.0052,0.0003</t>
-  </si>
-  <si>
-    <t>0.9756,0.0134,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.9804,0.0121,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9831,0.0106,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.5043,0.4943,0.0206,0.0003</t>
-  </si>
-  <si>
-    <t>0.5855,0.4029,0.0269,0.0006</t>
-  </si>
-  <si>
-    <t>0.4263,0.5492,0.0260,0.0004</t>
-  </si>
-  <si>
-    <t>0.5423,0.0114,0.5641,0.0003</t>
-  </si>
-  <si>
-    <t>0.9046,0.0679,0.0193,0.0003</t>
-  </si>
-  <si>
-    <t>0.9292,0.0321,0.0255,0.0003</t>
-  </si>
-  <si>
-    <t>0.9537,0.0287,0.0120,0.0002</t>
-  </si>
-  <si>
-    <t>0.5524,0.3454,0.0572,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0025,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.7923,0.0512,0.1223,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0035,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0367,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0040,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0148,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0080,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0062,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0073,0.0036,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.3736,0.0148,0.6769,0.0007</t>
-  </si>
-  <si>
-    <t>0.0928,0.0036,0.9380,0.0001</t>
-  </si>
-  <si>
-    <t>0.2657,0.0074,0.8043,0.0001</t>
-  </si>
-  <si>
-    <t>0.2879,0.0140,0.7612,0.0001</t>
-  </si>
-  <si>
-    <t>0.3558,0.0202,0.6709,0.0003</t>
-  </si>
-  <si>
-    <t>0.3371,0.0079,0.7291,0.0001</t>
-  </si>
-  <si>
-    <t>0.5620,0.0105,0.5049,0.0007</t>
-  </si>
-  <si>
-    <t>0.5592,0.0091,0.5203,0.0003</t>
-  </si>
-  <si>
-    <t>0.6546,0.2044,0.0653,0.0003</t>
-  </si>
-  <si>
-    <t>0.4937,0.3699,0.0496,0.0003</t>
-  </si>
-  <si>
-    <t>0.5739,0.3025,0.0463,0.0003</t>
-  </si>
-  <si>
-    <t>0.8082,0.1789,0.0211,0.0006</t>
-  </si>
-  <si>
-    <t>0.8092,0.1688,0.0215,0.0002</t>
-  </si>
-  <si>
-    <t>0.5068,0.0186,0.5525,0.0004</t>
-  </si>
-  <si>
-    <t>0.6572,0.0056,0.4241,0.0003</t>
-  </si>
-  <si>
-    <t>0.6813,0.0065,0.3832,0.0003</t>
-  </si>
-  <si>
-    <t>0.5336,0.0031,0.5756,0.0003</t>
-  </si>
-  <si>
-    <t>0.5336,0.0059,0.5677,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0414,0.0236,0.9488,0.0009</t>
-  </si>
-  <si>
-    <t>0.0048,0.2339,0.9650,0.0002</t>
-  </si>
-  <si>
-    <t>0.0073,0.0242,0.9879,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.1876,0.9892,0.0001</t>
-  </si>
-  <si>
-    <t>0.9741,0.0182,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.9463,0.0398,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9656,0.0258,0.0067,0.0004</t>
-  </si>
-  <si>
-    <t>0.9789,0.0175,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9768,0.0175,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.9783,0.0146,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.9811,0.0124,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.9826,0.0109,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.0277,0.0052,0.9766,0.0001</t>
-  </si>
-  <si>
-    <t>0.6310,0.0202,0.4042,0.0005</t>
-  </si>
-  <si>
-    <t>0.5658,0.0071,0.5453,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0260,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0188,0.0163,0.9777,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0029,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0067,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0033,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0046,0.0094,0.9933,0.0001</t>
-  </si>
-  <si>
-    <t>0.0088,0.0708,0.9777,0.0003</t>
-  </si>
-  <si>
-    <t>0.6531,0.0026,0.4571,0.0002</t>
-  </si>
-  <si>
-    <t>0.2697,0.0055,0.7966,0.0004</t>
-  </si>
-  <si>
-    <t>0.6190,0.0049,0.4535,0.0012</t>
-  </si>
-  <si>
-    <t>0.9771,0.0168,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.9845,0.0124,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9868,0.0108,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9819,0.0139,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9418,0.0471,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.9826,0.0149,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9807,0.0136,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.9810,0.0131,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.0186,0.4191,0.8205,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0050,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.2255,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.1329,0.0218,0.8633,0.0008</t>
-  </si>
-  <si>
-    <t>0.0014,0.0042,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0389,0.0060,0.9651,0.0003</t>
-  </si>
-  <si>
-    <t>0.3003,0.0030,0.7905,0.0001</t>
-  </si>
-  <si>
-    <t>0.0533,0.0299,0.9363,0.0006</t>
-  </si>
-  <si>
-    <t>0.7251,0.0097,0.3183,0.0016</t>
-  </si>
-  <si>
-    <t>0.1511,0.0280,0.0725,0.7745</t>
-  </si>
-  <si>
-    <t>0.5062,0.0062,0.2140,0.1277</t>
-  </si>
-  <si>
-    <t>0.0305,0.0022,0.0169,0.9776</t>
-  </si>
-  <si>
-    <t>0.0095,0.0018,0.0105,0.9932</t>
-  </si>
-  <si>
-    <t>0.6982,0.0198,0.2897,0.0036</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.6111,0.0086,0.4570,0.0016</t>
+  </si>
+  <si>
+    <t>0.5071,0.0063,0.1756,0.1282</t>
+  </si>
+  <si>
+    <t>0.7477,0.0221,0.2125,0.0096</t>
+  </si>
+  <si>
+    <t>0.6774,0.0071,0.2513,0.0202</t>
+  </si>
+  <si>
+    <t>0.9747,0.0158,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.9871,0.0099,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9841,0.0114,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.9891,0.0078,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9764,0.0217,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.9874,0.0109,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0077,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9889,0.0078,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.6209,0.0085,0.4568,0.0003</t>
+  </si>
+  <si>
+    <t>0.1036,0.0063,0.9251,0.0001</t>
+  </si>
+  <si>
+    <t>0.1591,0.0103,0.8777,0.0002</t>
+  </si>
+  <si>
+    <t>0.0126,0.0025,0.9897,0.0001</t>
+  </si>
+  <si>
+    <t>0.6107,0.0047,0.4904,0.0003</t>
+  </si>
+  <si>
+    <t>0.0048,0.9909,0.0065,0.0001</t>
+  </si>
+  <si>
+    <t>0.0095,0.9835,0.0098,0.0001</t>
+  </si>
+  <si>
+    <t>0.3185,0.7102,0.0175,0.0006</t>
+  </si>
+  <si>
+    <t>0.0283,0.9630,0.0097,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.9948,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.5370,0.0079,0.5512,0.0004</t>
+  </si>
+  <si>
+    <t>0.3852,0.0060,0.7031,0.0003</t>
+  </si>
+  <si>
+    <t>0.0066,0.0038,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.2122,0.0069,0.8451,0.0002</t>
+  </si>
+  <si>
+    <t>0.0194,0.0055,0.9821,0.0001</t>
+  </si>
+  <si>
+    <t>0.0157,0.0029,0.9847,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0052,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.2885,0.2841,0.2474,0.0014</t>
+  </si>
+  <si>
+    <t>0.4308,0.0160,0.6387,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1269,0.5280,0.2215,0.0010</t>
+  </si>
+  <si>
+    <t>0.6596,0.0456,0.2914,0.0010</t>
+  </si>
+  <si>
+    <t>0.0774,0.0255,0.9304,0.0002</t>
+  </si>
+  <si>
+    <t>0.6714,0.2250,0.0607,0.0008</t>
+  </si>
+  <si>
+    <t>0.0573,0.9204,0.0255,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.9644,0.3471,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.0577,0.9884,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.6948,0.9142,0.0003</t>
+  </si>
+  <si>
+    <t>0.0450,0.0190,0.9535,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.0278,0.9891,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9951,0.0228,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0297,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.6500,0.1120,0.1719,0.0220</t>
+  </si>
+  <si>
+    <t>0.0009,0.9963,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.9894,0.0187,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1487,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6323,0.9930,0.0000</t>
+  </si>
+  <si>
+    <t>0.0242,0.0129,0.9725,0.0003</t>
+  </si>
+  <si>
+    <t>0.0149,0.0014,0.9879,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0070,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0077,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.9455,0.0318,0.0152,0.0001</t>
+  </si>
+  <si>
+    <t>0.9022,0.0128,0.0878,0.0003</t>
+  </si>
+  <si>
+    <t>0.9602,0.0193,0.0135,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0567,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.9667,0.0192,0.0095,0.0002</t>
+  </si>
+  <si>
+    <t>0.9736,0.0186,0.0057,0.0002</t>
+  </si>
+  <si>
+    <t>0.9339,0.0445,0.0145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9894,0.7675,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0104,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0149,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8903,0.9895,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0061,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0511,0.8973,0.0413,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9976,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.4411,0.0071,0.6715,0.0002</t>
+  </si>
+  <si>
+    <t>0.1051,0.0217,0.9027,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0048,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9232,0.9825,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.8908,0.9426,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9906,0.2039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.3187,0.0000</t>
+  </si>
+  <si>
+    <t>0.6060,0.0051,0.3289,0.0209</t>
+  </si>
+  <si>
+    <t>0.0778,0.0063,0.0498,0.9116</t>
+  </si>
+  <si>
+    <t>0.3933,0.0052,0.0946,0.3311</t>
+  </si>
+  <si>
+    <t>0.4270,0.0068,0.1733,0.2198</t>
+  </si>
+  <si>
+    <t>0.4284,0.0075,0.1081,0.2953</t>
+  </si>
+  <si>
+    <t>0.0239,0.0031,0.0359,0.9746</t>
+  </si>
+  <si>
+    <t>0.0001,0.9701,0.8872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6877,0.9912,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8688,0.9662,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8358,0.9765,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.8959,0.9108,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9771,0.8798,0.0000</t>
+  </si>
+  <si>
+    <t>0.9900,0.0078,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9801,0.0132,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.9692,0.0259,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.9850,0.0114,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.9748,0.0171,0.0052,0.0003</t>
+  </si>
+  <si>
+    <t>0.9714,0.0241,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.9755,0.0191,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.9521,0.0388,0.0086,0.0002</t>
+  </si>
+  <si>
+    <t>0.9914,0.0053,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9844,0.0117,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.9882,0.0078,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9889,0.0079,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9886,0.0090,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9797,0.0183,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9848,0.0106,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.9875,0.0079,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0055,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.5212,0.0091,0.5394,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0021,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0416,0.9587,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.0301,0.9645,0.0069,0.0001</t>
+  </si>
+  <si>
+    <t>0.1102,0.8693,0.0224,0.0005</t>
+  </si>
+  <si>
+    <t>0.4628,0.4054,0.0437,0.0004</t>
+  </si>
+  <si>
+    <t>0.0195,0.9758,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.0131,0.9847,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.4495,0.4274,0.0526,0.0009</t>
+  </si>
+  <si>
+    <t>0.6628,0.0083,0.3911,0.0006</t>
+  </si>
+  <si>
+    <t>0.0519,0.0069,0.9584,0.0001</t>
+  </si>
+  <si>
+    <t>0.4477,0.0273,0.5640,0.0006</t>
+  </si>
+  <si>
+    <t>0.4529,0.0039,0.6653,0.0002</t>
+  </si>
+  <si>
+    <t>0.6147,0.0153,0.4008,0.0050</t>
+  </si>
+  <si>
+    <t>0.0006,0.9979,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.9908,0.0059,0.0005</t>
+  </si>
+  <si>
+    <t>0.1198,0.8597,0.0258,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.9987,0.0087,0.0000</t>
+  </si>
+  <si>
+    <t>0.2190,0.7171,0.0322,0.0003</t>
+  </si>
+  <si>
+    <t>0.6615,0.2386,0.0468,0.0004</t>
+  </si>
+  <si>
+    <t>0.4284,0.5197,0.0352,0.0009</t>
+  </si>
+  <si>
+    <t>0.9320,0.0283,0.0244,0.0001</t>
+  </si>
+  <si>
+    <t>0.9694,0.0146,0.0103,0.0002</t>
+  </si>
+  <si>
+    <t>0.9798,0.0134,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.9306,0.0330,0.0248,0.0004</t>
+  </si>
+  <si>
+    <t>0.9694,0.0221,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.9068,0.0429,0.0302,0.0002</t>
+  </si>
+  <si>
+    <t>0.9826,0.0128,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9780,0.0139,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.7131,0.9344,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.3035,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0111,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.2216,0.9726,0.0003</t>
+  </si>
+  <si>
+    <t>0.6767,0.0030,0.4206,0.0002</t>
+  </si>
+  <si>
+    <t>0.5660,0.0091,0.5152,0.0004</t>
+  </si>
+  <si>
+    <t>0.0562,0.0013,0.9631,0.0001</t>
+  </si>
+  <si>
+    <t>0.6296,0.0070,0.4366,0.0005</t>
+  </si>
+  <si>
+    <t>0.7013,0.0069,0.3041,0.0051</t>
+  </si>
+  <si>
+    <t>0.0024,0.0013,0.0082,0.9978</t>
+  </si>
+  <si>
+    <t>0.2005,0.0082,0.0837,0.6649</t>
+  </si>
+  <si>
+    <t>0.1341,0.0026,0.0330,0.8535</t>
+  </si>
+  <si>
+    <t>0.0000,0.8946,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.9568,0.0297,0.0096,0.0005</t>
+  </si>
+  <si>
+    <t>0.4154,0.1235,0.4447,0.0073</t>
+  </si>
+  <si>
+    <t>0.9533,0.0142,0.0215,0.0003</t>
+  </si>
+  <si>
+    <t>0.6251,0.2686,0.0486,0.0006</t>
+  </si>
+  <si>
+    <t>0.9368,0.0132,0.0358,0.0006</t>
+  </si>
+  <si>
+    <t>0.7573,0.0105,0.2665,0.0014</t>
+  </si>
+  <si>
+    <t>0.9596,0.0136,0.0155,0.0006</t>
+  </si>
+  <si>
+    <t>0.0119,0.0301,0.9828,0.0002</t>
+  </si>
+  <si>
+    <t>0.8585,0.0108,0.1223,0.0012</t>
+  </si>
+  <si>
+    <t>0.8828,0.0162,0.0974,0.0005</t>
+  </si>
+  <si>
+    <t>0.5118,0.2429,0.0842,0.0006</t>
+  </si>
+  <si>
+    <t>0.7859,0.0380,0.1476,0.0006</t>
+  </si>
+  <si>
+    <t>0.6520,0.0183,0.4054,0.0006</t>
+  </si>
+  <si>
+    <t>0.4993,0.1717,0.2114,0.0019</t>
+  </si>
+  <si>
+    <t>0.5494,0.0377,0.4064,0.0004</t>
+  </si>
+  <si>
+    <t>0.7128,0.0164,0.3075,0.0004</t>
+  </si>
+  <si>
+    <t>0.9836,0.0104,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9863,0.0080,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.9732,0.0159,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.9806,0.0083,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.9706,0.0173,0.0078,0.0002</t>
+  </si>
+  <si>
+    <t>0.9723,0.0174,0.0069,0.0002</t>
+  </si>
+  <si>
+    <t>0.9752,0.0157,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.9817,0.0106,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.5951,0.3671,0.0322,0.0006</t>
+  </si>
+  <si>
+    <t>0.7057,0.2577,0.0301,0.0005</t>
+  </si>
+  <si>
+    <t>0.4486,0.4973,0.0346,0.0005</t>
+  </si>
+  <si>
+    <t>0.5078,0.0179,0.5756,0.0002</t>
+  </si>
+  <si>
+    <t>0.7967,0.1820,0.0226,0.0004</t>
+  </si>
+  <si>
+    <t>0.8421,0.0327,0.1116,0.0005</t>
+  </si>
+  <si>
+    <t>0.8736,0.0732,0.0312,0.0002</t>
+  </si>
+  <si>
+    <t>0.6984,0.1613,0.0758,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.6591,0.0188,0.3927,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0083,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0487,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0110,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0307,0.9936,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0069,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0034,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.3657,0.0170,0.6735,0.0004</t>
+  </si>
+  <si>
+    <t>0.1053,0.0032,0.9294,0.0001</t>
+  </si>
+  <si>
+    <t>0.6392,0.0162,0.3827,0.0005</t>
+  </si>
+  <si>
+    <t>0.1824,0.0125,0.8522,0.0003</t>
+  </si>
+  <si>
+    <t>0.4668,0.0303,0.5107,0.0008</t>
+  </si>
+  <si>
+    <t>0.3760,0.0126,0.6700,0.0002</t>
+  </si>
+  <si>
+    <t>0.6055,0.0059,0.4784,0.0004</t>
+  </si>
+  <si>
+    <t>0.5111,0.0036,0.6221,0.0001</t>
+  </si>
+  <si>
+    <t>0.4592,0.4422,0.0543,0.0005</t>
+  </si>
+  <si>
+    <t>0.6045,0.2319,0.0609,0.0002</t>
+  </si>
+  <si>
+    <t>0.5936,0.2811,0.0537,0.0003</t>
+  </si>
+  <si>
+    <t>0.5849,0.4082,0.0279,0.0008</t>
+  </si>
+  <si>
+    <t>0.7022,0.2937,0.0258,0.0006</t>
+  </si>
+  <si>
+    <t>0.5263,0.0149,0.5385,0.0005</t>
+  </si>
+  <si>
+    <t>0.6569,0.0054,0.4256,0.0003</t>
+  </si>
+  <si>
+    <t>0.6956,0.0131,0.3211,0.0021</t>
+  </si>
+  <si>
+    <t>0.5609,0.0042,0.5403,0.0002</t>
+  </si>
+  <si>
+    <t>0.3030,0.0049,0.7897,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0021,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0129,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.2150,0.9570,0.0004</t>
+  </si>
+  <si>
+    <t>0.0088,0.1035,0.9714,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.3182,0.9773,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0095,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9414,0.0441,0.0105,0.0001</t>
+  </si>
+  <si>
+    <t>0.9718,0.0225,0.0050,0.0003</t>
+  </si>
+  <si>
+    <t>0.9353,0.0530,0.0109,0.0003</t>
+  </si>
+  <si>
+    <t>0.9659,0.0243,0.0072,0.0001</t>
+  </si>
+  <si>
+    <t>0.9787,0.0170,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.9736,0.0181,0.0056,0.0002</t>
+  </si>
+  <si>
+    <t>0.9825,0.0116,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.0640,0.0050,0.9514,0.0002</t>
+  </si>
+  <si>
+    <t>0.5981,0.0251,0.4170,0.0004</t>
+  </si>
+  <si>
+    <t>0.5796,0.0101,0.5209,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0055,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0557,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0181,0.0063,0.9833,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0027,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.0054,0.9940,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0020,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0044,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0072,0.0050,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.5890,0.0032,0.5297,0.0001</t>
+  </si>
+  <si>
+    <t>0.2147,0.0073,0.8269,0.0005</t>
+  </si>
+  <si>
+    <t>0.6262,0.0045,0.4649,0.0005</t>
+  </si>
+  <si>
+    <t>0.9623,0.0270,0.0080,0.0005</t>
+  </si>
+  <si>
+    <t>0.9691,0.0240,0.0059,0.0002</t>
+  </si>
+  <si>
+    <t>0.9855,0.0120,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.9744,0.0208,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.9674,0.0224,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.9718,0.0211,0.0056,0.0002</t>
+  </si>
+  <si>
+    <t>0.9802,0.0147,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.9833,0.0106,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.0072,0.9901,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0193,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0469,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0824,0.0251,0.9011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0034,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0366,0.0027,0.9700,0.0005</t>
+  </si>
+  <si>
+    <t>0.1589,0.0042,0.8889,0.0001</t>
+  </si>
+  <si>
+    <t>0.0343,0.0188,0.9607,0.0014</t>
+  </si>
+  <si>
+    <t>0.7551,0.0087,0.2806,0.0015</t>
+  </si>
+  <si>
+    <t>0.2423,0.0248,0.0883,0.5788</t>
+  </si>
+  <si>
+    <t>0.4702,0.0054,0.2138,0.1512</t>
+  </si>
+  <si>
+    <t>0.0572,0.0024,0.0368,0.9365</t>
+  </si>
+  <si>
+    <t>0.0106,0.0023,0.0210,0.9906</t>
+  </si>
+  <si>
+    <t>0.7299,0.0297,0.2242,0.0043</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2407,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2505,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2645,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2995,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3037,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3051,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3065,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3499,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3989,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5053,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5473,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
